--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,855 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124968696</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sjöån, Sjöån, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>495755</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6907825</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124969190</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sjöån, Sjöån, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>495762</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6908016</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124967917</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sjöån, Sjöån, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>495627</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6907768</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124964829</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98124</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sjöån, Sjöån, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>495567</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6907661</v>
+      </c>
+      <c r="S6" t="n">
+        <v>18</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124967710</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sjöån, Sjöån, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>495638</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6907802</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124967791</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sjöån, Sjöån, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>495628</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6907779</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124967768</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sjöån, Sjöån, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>495646</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6907794</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124966571</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sjöån, Sjöån, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>495604</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6907750</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joakim Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joakim Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124968696</v>
+        <v>124964829</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>98124</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,41 +816,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495755</v>
+        <v>495567</v>
       </c>
       <c r="R3" t="n">
-        <v>6907825</v>
+        <v>6907661</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -906,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124969190</v>
+        <v>124966571</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,36 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495762</v>
+        <v>495604</v>
       </c>
       <c r="R4" t="n">
-        <v>6908016</v>
+        <v>6907750</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,9 +992,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124967917</v>
+        <v>124969190</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,41 +1043,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495627</v>
+        <v>495762</v>
       </c>
       <c r="R5" t="n">
-        <v>6907768</v>
+        <v>6908016</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124964829</v>
+        <v>124967917</v>
       </c>
       <c r="B6" t="n">
-        <v>98124</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,50 +1155,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495567</v>
+        <v>495627</v>
       </c>
       <c r="R6" t="n">
-        <v>6907661</v>
+        <v>6907768</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1333,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124967791</v>
+        <v>124968696</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495628</v>
+        <v>495755</v>
       </c>
       <c r="R8" t="n">
-        <v>6907779</v>
+        <v>6907825</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1537,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124966571</v>
+        <v>124967791</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1570,24 +1584,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495604</v>
+        <v>495628</v>
       </c>
       <c r="R10" t="n">
-        <v>6907750</v>
+        <v>6907779</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1614,19 +1624,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,12 +1641,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124964829</v>
+        <v>124967768</v>
       </c>
       <c r="B3" t="n">
-        <v>98124</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,50 +816,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495567</v>
+        <v>495646</v>
       </c>
       <c r="R3" t="n">
-        <v>6907661</v>
+        <v>6907794</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -915,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124966571</v>
+        <v>124969190</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +918,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495604</v>
+        <v>495762</v>
       </c>
       <c r="R4" t="n">
-        <v>6907750</v>
+        <v>6908016</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,19 +989,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1006,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124969190</v>
+        <v>124964829</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>98124</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,32 +1034,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1081,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495762</v>
+        <v>495567</v>
       </c>
       <c r="R5" t="n">
-        <v>6908016</v>
+        <v>6907661</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1143,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124967917</v>
+        <v>124967791</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1183,13 +1169,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495627</v>
+        <v>495628</v>
       </c>
       <c r="R6" t="n">
-        <v>6907768</v>
+        <v>6907779</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124967710</v>
+        <v>124968696</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1243,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495638</v>
+        <v>495755</v>
       </c>
       <c r="R7" t="n">
-        <v>6907802</v>
+        <v>6907825</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1347,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124968696</v>
+        <v>124967710</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1345,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495755</v>
+        <v>495638</v>
       </c>
       <c r="R8" t="n">
-        <v>6907825</v>
+        <v>6907802</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1449,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124967768</v>
+        <v>124966571</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1482,20 +1468,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495646</v>
+        <v>495604</v>
       </c>
       <c r="R9" t="n">
-        <v>6907794</v>
+        <v>6907750</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,9 +1512,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,19 +1539,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124967791</v>
+        <v>124967917</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1591,13 +1591,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495628</v>
+        <v>495627</v>
       </c>
       <c r="R10" t="n">
-        <v>6907779</v>
+        <v>6907768</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124967768</v>
+        <v>124966571</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -837,20 +837,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495646</v>
+        <v>495604</v>
       </c>
       <c r="R3" t="n">
-        <v>6907794</v>
+        <v>6907750</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,9 +881,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,22 +908,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124969190</v>
+        <v>124967791</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,51 +932,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495762</v>
+        <v>495628</v>
       </c>
       <c r="R4" t="n">
-        <v>6908016</v>
+        <v>6907779</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124964829</v>
+        <v>124968696</v>
       </c>
       <c r="B5" t="n">
-        <v>98124</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,50 +1034,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495567</v>
+        <v>495755</v>
       </c>
       <c r="R5" t="n">
-        <v>6907661</v>
+        <v>6907825</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124967791</v>
+        <v>124967917</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1169,13 +1164,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495628</v>
+        <v>495627</v>
       </c>
       <c r="R6" t="n">
-        <v>6907779</v>
+        <v>6907768</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124968696</v>
+        <v>124967768</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,25 +1238,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495755</v>
+        <v>495646</v>
       </c>
       <c r="R7" t="n">
-        <v>6907825</v>
+        <v>6907794</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1333,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124967710</v>
+        <v>124964829</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98124</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,41 +1340,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495638</v>
+        <v>495567</v>
       </c>
       <c r="R8" t="n">
-        <v>6907802</v>
+        <v>6907661</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124966571</v>
+        <v>124969190</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,30 +1451,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1479,13 +1489,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495604</v>
+        <v>495762</v>
       </c>
       <c r="R9" t="n">
-        <v>6907750</v>
+        <v>6908016</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,19 +1522,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,19 +1539,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124967917</v>
+        <v>124967710</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1591,13 +1591,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495627</v>
+        <v>495638</v>
       </c>
       <c r="R10" t="n">
-        <v>6907768</v>
+        <v>6907802</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124966571</v>
+        <v>124967791</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -837,24 +837,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495604</v>
+        <v>495628</v>
       </c>
       <c r="R3" t="n">
-        <v>6907750</v>
+        <v>6907779</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,19 +877,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,22 +894,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124967791</v>
+        <v>124969190</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,41 +918,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495628</v>
+        <v>495762</v>
       </c>
       <c r="R4" t="n">
-        <v>6907779</v>
+        <v>6908016</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124968696</v>
+        <v>124967710</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495755</v>
+        <v>495638</v>
       </c>
       <c r="R5" t="n">
-        <v>6907825</v>
+        <v>6907802</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1124,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124967917</v>
+        <v>124964829</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98124</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,41 +1132,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495627</v>
+        <v>495567</v>
       </c>
       <c r="R6" t="n">
-        <v>6907768</v>
+        <v>6907661</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124967768</v>
+        <v>124968696</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,25 +1243,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495646</v>
+        <v>495755</v>
       </c>
       <c r="R7" t="n">
-        <v>6907794</v>
+        <v>6907825</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1328,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124964829</v>
+        <v>124966571</v>
       </c>
       <c r="B8" t="n">
-        <v>98124</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,35 +1345,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495567</v>
+        <v>495604</v>
       </c>
       <c r="R8" t="n">
-        <v>6907661</v>
+        <v>6907750</v>
       </c>
       <c r="S8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,9 +1410,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,22 +1437,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124969190</v>
+        <v>124967917</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,51 +1461,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495762</v>
+        <v>495627</v>
       </c>
       <c r="R9" t="n">
-        <v>6908016</v>
+        <v>6907768</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124967710</v>
+        <v>124967768</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495638</v>
+        <v>495646</v>
       </c>
       <c r="R10" t="n">
-        <v>6907802</v>
+        <v>6907794</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124967710</v>
+        <v>124968696</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495638</v>
+        <v>495755</v>
       </c>
       <c r="R5" t="n">
-        <v>6907802</v>
+        <v>6907825</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124964829</v>
+        <v>124966571</v>
       </c>
       <c r="B6" t="n">
-        <v>98124</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,35 +1132,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1169,13 +1164,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495567</v>
+        <v>495604</v>
       </c>
       <c r="R6" t="n">
-        <v>6907661</v>
+        <v>6907750</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,9 +1197,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,22 +1224,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124968696</v>
+        <v>124967768</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,25 +1248,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495755</v>
+        <v>495646</v>
       </c>
       <c r="R7" t="n">
-        <v>6907825</v>
+        <v>6907794</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1333,7 +1338,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124966571</v>
+        <v>124967917</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1366,21 +1371,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495604</v>
+        <v>495627</v>
       </c>
       <c r="R8" t="n">
-        <v>6907750</v>
+        <v>6907768</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,19 +1411,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,19 +1428,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124967917</v>
+        <v>124967710</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1489,13 +1480,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495627</v>
+        <v>495638</v>
       </c>
       <c r="R9" t="n">
-        <v>6907768</v>
+        <v>6907802</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124967768</v>
+        <v>124964829</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>98124</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,41 +1554,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495646</v>
+        <v>495567</v>
       </c>
       <c r="R10" t="n">
-        <v>6907794</v>
+        <v>6907661</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124967791</v>
+        <v>124968696</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,25 +816,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495628</v>
+        <v>495755</v>
       </c>
       <c r="R3" t="n">
-        <v>6907779</v>
+        <v>6907825</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124969190</v>
+        <v>124967768</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,51 +918,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495762</v>
+        <v>495646</v>
       </c>
       <c r="R4" t="n">
-        <v>6908016</v>
+        <v>6907794</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124968696</v>
+        <v>124967710</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495755</v>
+        <v>495638</v>
       </c>
       <c r="R5" t="n">
-        <v>6907825</v>
+        <v>6907802</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1236,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124967768</v>
+        <v>124969190</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,41 +1238,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495646</v>
+        <v>495762</v>
       </c>
       <c r="R7" t="n">
-        <v>6907794</v>
+        <v>6908016</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124967917</v>
+        <v>124967791</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495627</v>
+        <v>495628</v>
       </c>
       <c r="R8" t="n">
-        <v>6907768</v>
+        <v>6907779</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124967710</v>
+        <v>124964829</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>98124</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,41 +1452,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495638</v>
+        <v>495567</v>
       </c>
       <c r="R9" t="n">
-        <v>6907802</v>
+        <v>6907661</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124964829</v>
+        <v>124967917</v>
       </c>
       <c r="B10" t="n">
-        <v>98124</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,50 +1563,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495567</v>
+        <v>495627</v>
       </c>
       <c r="R10" t="n">
-        <v>6907661</v>
+        <v>6907768</v>
       </c>
       <c r="S10" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124968696</v>
+        <v>124964829</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>98124</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,41 +816,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495755</v>
+        <v>495567</v>
       </c>
       <c r="R3" t="n">
-        <v>6907825</v>
+        <v>6907661</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -906,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124967768</v>
+        <v>124968696</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,25 +927,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495646</v>
+        <v>495755</v>
       </c>
       <c r="R4" t="n">
-        <v>6907794</v>
+        <v>6907825</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1008,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124967710</v>
+        <v>124967768</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1048,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495638</v>
+        <v>495646</v>
       </c>
       <c r="R5" t="n">
-        <v>6907802</v>
+        <v>6907794</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1110,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124966571</v>
+        <v>124967791</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1143,24 +1152,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495604</v>
+        <v>495628</v>
       </c>
       <c r="R6" t="n">
-        <v>6907750</v>
+        <v>6907779</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,19 +1192,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,22 +1209,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124969190</v>
+        <v>124967917</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,51 +1233,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495762</v>
+        <v>495627</v>
       </c>
       <c r="R7" t="n">
-        <v>6908016</v>
+        <v>6907768</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124967791</v>
+        <v>124966571</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1371,20 +1356,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495628</v>
+        <v>495604</v>
       </c>
       <c r="R8" t="n">
-        <v>6907779</v>
+        <v>6907750</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,9 +1400,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,22 +1427,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124964829</v>
+        <v>124967710</v>
       </c>
       <c r="B9" t="n">
-        <v>98124</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,50 +1451,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495567</v>
+        <v>495638</v>
       </c>
       <c r="R9" t="n">
-        <v>6907661</v>
+        <v>6907802</v>
       </c>
       <c r="S9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124967917</v>
+        <v>124969190</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,41 +1553,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495627</v>
+        <v>495762</v>
       </c>
       <c r="R10" t="n">
-        <v>6907768</v>
+        <v>6908016</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124964829</v>
+        <v>124966571</v>
       </c>
       <c r="B3" t="n">
-        <v>98124</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,35 +816,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -853,13 +848,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495567</v>
+        <v>495604</v>
       </c>
       <c r="R3" t="n">
-        <v>6907661</v>
+        <v>6907750</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,9 +881,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,22 +908,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124968696</v>
+        <v>124967768</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,25 +932,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495755</v>
+        <v>495646</v>
       </c>
       <c r="R4" t="n">
-        <v>6907825</v>
+        <v>6907794</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1017,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124967768</v>
+        <v>124968696</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1034,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495646</v>
+        <v>495755</v>
       </c>
       <c r="R5" t="n">
-        <v>6907794</v>
+        <v>6907825</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1119,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124967791</v>
+        <v>124967710</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1159,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495628</v>
+        <v>495638</v>
       </c>
       <c r="R6" t="n">
-        <v>6907779</v>
+        <v>6907802</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1323,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124966571</v>
+        <v>124969190</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,30 +1340,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1367,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495604</v>
+        <v>495762</v>
       </c>
       <c r="R8" t="n">
-        <v>6907750</v>
+        <v>6908016</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,19 +1411,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,19 +1428,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124967710</v>
+        <v>124967791</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1479,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495638</v>
+        <v>495628</v>
       </c>
       <c r="R9" t="n">
-        <v>6907802</v>
+        <v>6907779</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1541,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124969190</v>
+        <v>124964829</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>98124</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,32 +1558,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1591,13 +1591,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495762</v>
+        <v>495567</v>
       </c>
       <c r="R10" t="n">
-        <v>6908016</v>
+        <v>6907661</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124966571</v>
+        <v>124969190</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,30 +816,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -848,13 +854,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495604</v>
+        <v>495762</v>
       </c>
       <c r="R3" t="n">
-        <v>6907750</v>
+        <v>6908016</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,19 +887,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,19 +904,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124967768</v>
+        <v>124967917</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -960,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495646</v>
+        <v>495627</v>
       </c>
       <c r="R4" t="n">
-        <v>6907794</v>
+        <v>6907768</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124968696</v>
+        <v>124966571</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,41 +1030,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495755</v>
+        <v>495604</v>
       </c>
       <c r="R5" t="n">
-        <v>6907825</v>
+        <v>6907750</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,9 +1095,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,22 +1122,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124967710</v>
+        <v>124964829</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98124</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,41 +1146,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495638</v>
+        <v>495567</v>
       </c>
       <c r="R6" t="n">
-        <v>6907802</v>
+        <v>6907661</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124967917</v>
+        <v>124967710</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1266,13 +1285,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495627</v>
+        <v>495638</v>
       </c>
       <c r="R7" t="n">
-        <v>6907768</v>
+        <v>6907802</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124969190</v>
+        <v>124967768</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,51 +1359,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495762</v>
+        <v>495646</v>
       </c>
       <c r="R8" t="n">
-        <v>6908016</v>
+        <v>6907794</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124964829</v>
+        <v>124968696</v>
       </c>
       <c r="B10" t="n">
-        <v>98124</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,50 +1563,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495567</v>
+        <v>495755</v>
       </c>
       <c r="R10" t="n">
-        <v>6907661</v>
+        <v>6907825</v>
       </c>
       <c r="S10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124969190</v>
+        <v>124968696</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,51 +816,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495762</v>
+        <v>495755</v>
       </c>
       <c r="R3" t="n">
-        <v>6908016</v>
+        <v>6907825</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -916,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124967917</v>
+        <v>124967710</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -956,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495627</v>
+        <v>495638</v>
       </c>
       <c r="R4" t="n">
-        <v>6907768</v>
+        <v>6907802</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124966571</v>
+        <v>124967791</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1051,24 +1041,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495604</v>
+        <v>495628</v>
       </c>
       <c r="R5" t="n">
-        <v>6907750</v>
+        <v>6907779</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,19 +1081,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,22 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124964829</v>
+        <v>124969190</v>
       </c>
       <c r="B6" t="n">
-        <v>98124</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,31 +1126,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,13 +1160,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495567</v>
+        <v>495762</v>
       </c>
       <c r="R6" t="n">
-        <v>6907661</v>
+        <v>6908016</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124967710</v>
+        <v>124964829</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>98124</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,41 +1234,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495638</v>
+        <v>495567</v>
       </c>
       <c r="R7" t="n">
-        <v>6907802</v>
+        <v>6907661</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,7 +1333,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124967768</v>
+        <v>124967917</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1387,13 +1373,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495646</v>
+        <v>495627</v>
       </c>
       <c r="R8" t="n">
-        <v>6907794</v>
+        <v>6907768</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124967791</v>
+        <v>124967768</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1489,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495628</v>
+        <v>495646</v>
       </c>
       <c r="R9" t="n">
-        <v>6907779</v>
+        <v>6907794</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1551,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124968696</v>
+        <v>124966571</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,41 +1549,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495755</v>
+        <v>495604</v>
       </c>
       <c r="R10" t="n">
-        <v>6907825</v>
+        <v>6907750</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1624,9 +1614,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,12 +1641,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124968696</v>
+        <v>124967917</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,25 +816,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495755</v>
+        <v>495627</v>
       </c>
       <c r="R3" t="n">
-        <v>6907825</v>
+        <v>6907768</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124967710</v>
+        <v>124969190</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,41 +918,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495638</v>
+        <v>495762</v>
       </c>
       <c r="R4" t="n">
-        <v>6907802</v>
+        <v>6908016</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +1021,7 @@
         <v>124967791</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1110,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124969190</v>
+        <v>124968696</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>78684</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,51 +1132,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495762</v>
+        <v>495755</v>
       </c>
       <c r="R6" t="n">
-        <v>6908016</v>
+        <v>6907825</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124964829</v>
+        <v>124967710</v>
       </c>
       <c r="B7" t="n">
-        <v>98124</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,50 +1234,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495567</v>
+        <v>495638</v>
       </c>
       <c r="R7" t="n">
-        <v>6907661</v>
+        <v>6907802</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124967917</v>
+        <v>124964829</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98292</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,41 +1336,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495627</v>
+        <v>495567</v>
       </c>
       <c r="R8" t="n">
-        <v>6907768</v>
+        <v>6907661</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>124967768</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>124966571</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124967917</v>
+        <v>124967768</v>
       </c>
       <c r="B3" t="n">
         <v>98269</v>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495627</v>
+        <v>495646</v>
       </c>
       <c r="R3" t="n">
-        <v>6907768</v>
+        <v>6907794</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124969190</v>
+        <v>124968696</v>
       </c>
       <c r="B4" t="n">
-        <v>56836</v>
+        <v>78684</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,51 +918,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495762</v>
+        <v>495755</v>
       </c>
       <c r="R4" t="n">
-        <v>6908016</v>
+        <v>6907825</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124967791</v>
+        <v>124967917</v>
       </c>
       <c r="B5" t="n">
         <v>98269</v>
@@ -1058,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495628</v>
+        <v>495627</v>
       </c>
       <c r="R5" t="n">
-        <v>6907779</v>
+        <v>6907768</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124968696</v>
+        <v>124967710</v>
       </c>
       <c r="B6" t="n">
-        <v>78684</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495755</v>
+        <v>495638</v>
       </c>
       <c r="R6" t="n">
-        <v>6907825</v>
+        <v>6907802</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1222,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124967710</v>
+        <v>124967791</v>
       </c>
       <c r="B7" t="n">
         <v>98269</v>
@@ -1262,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495638</v>
+        <v>495628</v>
       </c>
       <c r="R7" t="n">
-        <v>6907802</v>
+        <v>6907779</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1435,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124967768</v>
+        <v>124969190</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,41 +1437,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495646</v>
+        <v>495762</v>
       </c>
       <c r="R9" t="n">
-        <v>6907794</v>
+        <v>6908016</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124967791</v>
+        <v>124969190</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,41 +1224,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495628</v>
+        <v>495762</v>
       </c>
       <c r="R7" t="n">
-        <v>6907779</v>
+        <v>6908016</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1425,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124969190</v>
+        <v>124967791</v>
       </c>
       <c r="B9" t="n">
-        <v>56836</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,51 +1447,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495762</v>
+        <v>495628</v>
       </c>
       <c r="R9" t="n">
-        <v>6908016</v>
+        <v>6907779</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 36954-2020 artfynd.xlsx
+++ b/artfynd/A 36954-2020 artfynd.xlsx
@@ -804,37 +804,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124967768</v>
+        <v>124968696</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495646</v>
+        <v>495755</v>
       </c>
       <c r="R3" t="n">
-        <v>6907794</v>
+        <v>6907825</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -906,37 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124968696</v>
+        <v>124967710</v>
       </c>
       <c r="B4" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495755</v>
+        <v>495638</v>
       </c>
       <c r="R4" t="n">
-        <v>6907825</v>
+        <v>6907802</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1008,16 +998,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124967917</v>
+        <v>124967791</v>
       </c>
       <c r="B5" t="n">
         <v>98269</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1048,13 +1033,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495627</v>
+        <v>495628</v>
       </c>
       <c r="R5" t="n">
-        <v>6907768</v>
+        <v>6907779</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,53 +1095,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124967710</v>
+        <v>124964829</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495638</v>
+        <v>495567</v>
       </c>
       <c r="R6" t="n">
-        <v>6907802</v>
+        <v>6907661</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,11 +1206,6 @@
       <c r="B7" t="n">
         <v>56836</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1324,62 +1308,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124964829</v>
+        <v>124967917</v>
       </c>
       <c r="B8" t="n">
-        <v>98292</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495567</v>
+        <v>495627</v>
       </c>
       <c r="R8" t="n">
-        <v>6907661</v>
+        <v>6907768</v>
       </c>
       <c r="S8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,16 +1405,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124967791</v>
+        <v>124967768</v>
       </c>
       <c r="B9" t="n">
         <v>98269</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1475,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495628</v>
+        <v>495646</v>
       </c>
       <c r="R9" t="n">
-        <v>6907779</v>
+        <v>6907794</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1541,11 +1506,6 @@
       </c>
       <c r="B10" t="n">
         <v>98269</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
